--- a/stories/arbres/TREE-SAN-016.xlsx
+++ b/stories/arbres/TREE-SAN-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé est dans le jardin. Un petit écran est sur le banc. Papa s'assoit. Maman arrive. L'adulte dit fini. Zoé va éteindre. Puis elle prend un autre jeu, dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le chat du jardin passe. Papa dit : fini. L'adulte dit fini. Zoé éteint l'écran. Elle le pose. Papa dit : un autre jeu. Zoé cherche dans l'herbe.</t>
+          <t>Le chat du jardin passe. Fini. L'adulte dit fini. Zoé éteint l'écran. Elle le pose. Un autre jeu. Zoé cherche dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,15 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat du jardin passe.
+papa|Fini. L'adulte dit fini.
+narrateur|Zoé éteint l'écran. Elle le pose.
+papa|Un autre jeu.
+narrateur|Zoé cherche dans l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Zoé ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a éteint. L'adulte a dit fini. Un autre jeu commence, au jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2227,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va au bac à sable. L'écran est éteint. L'adulte a dit fini. Un autre jeu : creuser. Le chat s'éloigne.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2589,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Seau rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu au bac.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Seau bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle creuse.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Seau vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Le sable est chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé gravit le toboggan. L'écran est éteint. L'adulte a dit fini. Un autre jeu : glisser. Papa la voit.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3953,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4122,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Manteau rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle glisse.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4289,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4456,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Manteau bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Papa attend en bas.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4623,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4790,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Manteau vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle rit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé se balance. L'écran est éteint. L'adulte a dit fini. Un autre jeu. Maman pousse tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5315,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5341,6 +5482,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nœud rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Ça va, ça vient.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5649,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5816,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nœud bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Maman pousse.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5983,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6150,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nœud vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle chante.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6317,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6346,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Le chien du voisin reste loin, avec son maître. Maman dit : fini. L'adulte dit fini. Zoé éteint. Elle range l'écran dans le sac. Maman dit : un autre jeu.</t>
+          <t>Le chien du voisin reste loin, avec son maître. Fini. L'adulte dit fini. Zoé éteint. Elle range l'écran dans le sac. Un autre jeu.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6484,14 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien du voisin reste loin, avec son maître.
+maman|Fini. L'adulte dit fini.
+narrateur|Zoé éteint. Elle range l'écran dans le sac.
+maman|Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6668,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Zoé ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6841,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a éteint. L'adulte a dit fini. Le chien reste loin. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6845,6 +7034,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
     </row>
@@ -7009,6 +7203,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Zoé creuse. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7396,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7565,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Seau rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7732,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7899,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Seau bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8066,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8233,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Seau vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8400,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8567,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Au toboggan, Zoé attend. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8760,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8929,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Bonnet rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9096,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9263,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Bonnet bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9430,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9333,6 +9597,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Bonnet vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9764,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9931,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|À la balançoire, Zoé s'assoit. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10124,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10293,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Chaussures rouges. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10460,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10627,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Chaussures bleues. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10794,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10961,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Chaussures vertes. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11128,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10843,7 +11157,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Une poule picore au fond. Papa dit : fini. L'adulte dit fini. Zoé éteint. L'écran devient noir. Papa dit : un autre jeu, maintenant.</t>
+          <t>Une poule picore au fond. Fini. L'adulte dit fini. Zoé éteint. L'écran devient noir. Un autre jeu, maintenant.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10981,6 +11295,14 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Une poule picore au fond.
+papa|Fini. L'adulte dit fini.
+narrateur|Zoé éteint. L'écran devient noir.
+papa|Un autre jeu, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11483,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|L'adulte dit fini. Que fait Zoé ?</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11656,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a éteint. L'adulte a dit fini. La poule picore. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11517,6 +11849,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
     </row>
@@ -11681,6 +12018,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé empile du sable. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12211,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12380,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Moule rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12547,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12714,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Moule bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12881,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13048,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Moule vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13215,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13382,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé glisse. L'écran est éteint. L'adulte a dit fini. Un autre jeu. Maman clapote.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13575,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13744,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Collant rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13911,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14078,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Collant bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14245,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14412,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Collant vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14579,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14746,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé se balance et compte. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14515,6 +14937,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14677,6 +15104,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Fil rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14839,6 +15271,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15001,6 +15438,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Fil bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15163,6 +15605,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15325,6 +15772,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Fil vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15487,6 +15939,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15505,7 +15962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15585,6 +16042,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>ch3C2: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-016.xlsx
+++ b/stories/arbres/TREE-SAN-016.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Zoé est dans le jardin. Un petit écran est sur le banc. Papa s'assoit. Maman arrive. L'adulte dit fini. Zoé va éteindre. Puis elle prend un autre jeu, dehors.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1518,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1696,7 @@
 narrateur|Zoé cherche dans l'herbe.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1880,7 @@
           <t>narrateur|Papa dit fini. Que fait Zoé ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
           <t>narrateur|Zoé a éteint. L'adulte a dit fini. Un autre jeu commence, au jardin.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2248,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2416,7 @@
           <t>narrateur|Zoé va au bac à sable. L'écran est éteint. L'adulte a dit fini. Un autre jeu : creuser. Le chat s'éloigne.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2612,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2780,7 @@
           <t>narrateur|Seau rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu au bac.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3116,7 @@
           <t>narrateur|Seau bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle creuse.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3452,7 @@
           <t>narrateur|Seau vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Le sable est chaud.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3788,7 @@
           <t>narrateur|Zoé gravit le toboggan. L'écran est éteint. L'adulte a dit fini. Un autre jeu : glisser. Papa la voit.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3960,6 +3984,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4127,6 +4152,7 @@
           <t>narrateur|Manteau rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle glisse.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4294,6 +4320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4461,6 +4488,7 @@
           <t>narrateur|Manteau bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Papa attend en bas.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4628,6 +4656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4824,7 @@
           <t>narrateur|Manteau vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle rit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +4992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5160,7 @@
           <t>narrateur|Zoé se balance. L'écran est éteint. L'adulte a dit fini. Un autre jeu. Maman pousse tout doux.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5320,6 +5352,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5487,6 +5520,7 @@
           <t>narrateur|Nœud rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Ça va, ça vient.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5654,6 +5688,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5821,6 +5856,7 @@
           <t>narrateur|Nœud bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Maman pousse.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5988,6 +6024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6155,6 +6192,7 @@
           <t>narrateur|Nœud vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu. Elle chante.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6322,6 +6360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6492,6 +6531,11 @@
 maman|Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6675,6 +6719,7 @@
           <t>narrateur|Maman dit fini. Que fait Zoé ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6846,6 +6891,11 @@
           <t>narrateur|Zoé a éteint. L'adulte a dit fini. Le chien reste loin. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7041,6 +7091,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7208,6 +7259,7 @@
           <t>narrateur|Au bac, Zoé creuse. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7403,6 +7455,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7570,6 +7623,7 @@
           <t>narrateur|Seau rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7737,6 +7791,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7904,6 +7959,7 @@
           <t>narrateur|Seau bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8071,6 +8127,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8238,6 +8295,7 @@
           <t>narrateur|Seau vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8405,6 +8463,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8572,6 +8631,7 @@
           <t>narrateur|Au toboggan, Zoé attend. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8767,6 +8827,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8934,6 +8995,7 @@
           <t>narrateur|Bonnet rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9101,6 +9163,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9268,6 +9331,7 @@
           <t>narrateur|Bonnet bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9435,6 +9499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9602,6 +9667,7 @@
           <t>narrateur|Bonnet vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9769,6 +9835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9936,6 +10003,7 @@
           <t>narrateur|À la balançoire, Zoé s'assoit. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10131,6 +10199,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10298,6 +10367,7 @@
           <t>narrateur|Chaussures rouges. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10465,6 +10535,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10632,6 +10703,7 @@
           <t>narrateur|Chaussures bleues. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10799,6 +10871,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10966,6 +11039,7 @@
           <t>narrateur|Chaussures vertes. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11133,6 +11207,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11303,6 +11378,7 @@
 papa|Un autre jeu, maintenant.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11490,6 +11566,7 @@
           <t>narrateur|L'adulte dit fini. Que fait Zoé ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11661,6 +11738,7 @@
           <t>narrateur|Zoé a éteint. L'adulte a dit fini. La poule picore. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11856,6 +11934,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12023,6 +12102,7 @@
           <t>narrateur|Zoé empile du sable. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12218,6 +12298,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12385,6 +12466,7 @@
           <t>narrateur|Moule rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12552,6 +12634,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12719,6 +12802,7 @@
           <t>narrateur|Moule bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12886,6 +12970,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13053,6 +13138,7 @@
           <t>narrateur|Moule vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13220,6 +13306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13387,6 +13474,7 @@
           <t>narrateur|Zoé glisse. L'écran est éteint. L'adulte a dit fini. Un autre jeu. Maman clapote.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13582,6 +13670,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13749,6 +13838,7 @@
           <t>narrateur|Collant rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13916,6 +14006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14083,6 +14174,7 @@
           <t>narrateur|Collant bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14250,6 +14342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14417,6 +14510,7 @@
           <t>narrateur|Collant vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14584,6 +14678,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14751,6 +14846,7 @@
           <t>narrateur|Zoé se balance et compte. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14942,6 +15038,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15109,6 +15206,7 @@
           <t>narrateur|Fil rouge. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15276,6 +15374,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15443,6 +15542,7 @@
           <t>narrateur|Fil bleu. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15610,6 +15710,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15777,6 +15878,7 @@
           <t>narrateur|Fil vert. Zoé a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15944,6 +16046,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15962,7 +16065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16049,6 +16152,20 @@
       <c r="A12" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16063,7 +16180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16250,6 +16367,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
